--- a/previsionnel_2026.xlsx
+++ b/previsionnel_2026.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Juillet" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Août" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Septembre" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Octobre" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -461,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -545,6 +546,22 @@
       </c>
       <c r="D6" s="3" t="n">
         <v>6009.96</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>110752.15</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>15909.5</v>
       </c>
     </row>
   </sheetData>
@@ -8540,4 +8557,3604 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I103"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Prévisionnel pondéré — Octobre 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Capturé le 01/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Ticket CA</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Prévision brute (€)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Niveau de confiance</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Taux</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Prévision pondérée (€)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PDMDEP-35902</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>(non assigné)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>COMMUNE DE SETE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Abonnement Publication des actes</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>895</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PDMDEP-33440</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>8348</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>4174</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PDMDEP-32669</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>COMMUNE DE LA GARDE</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Migration Placier</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>2614.5</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>2222.32</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PDMDEP-33526</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VILLE DE MONTREUIL</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PDMDEP-32470</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NANTES METROPOLE - VDC</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Migration GEODP 1 vers GEODP 2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>6208</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Basse</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>931.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PDMDEP-33509</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mairie de Carcès </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>1221</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>610.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PDMDEP-32128</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>COMMUNE DE SARAN</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>1050</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33021</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE GRASSE</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Migration GeODP + Module Terrasse + formation sur site</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>1618.5</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Basse</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>242.77</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PDMDEP-33272</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MAIRIE DE CAPBRETON</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PDMDEP-31658</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MAIRIE DE GUILLESTRE</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>GeoDP Placier</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>172.97</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PDMDEP-31821</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>COMMUNE PROVINS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Migration V2 classique</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>1050</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Basse</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>157.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PDMDEP-32002</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Commune de Cluny</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>285</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>142.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PDMDEP-31045</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Migration V2 classique + abo CB</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>127.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PDMDEP-30335</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>COMMUNE DE ALENCON</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Migration 1 activité GEODP2</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PDMDEP-31360</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Migration vers GeoDP V2</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PDMDEP-34326</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Commune de Mouscron (BE)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Migration GEODP Placier</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>461.7</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PDMDEP-34310</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>COMMUNE DE GAP</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Migration Placier + ODP</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>4150</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PDMDEP-34258</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>COMMUNE DE VIENNE</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Migration Placier et ODP </t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>4254.4</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PDMDEP-34227</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Migration GEODP 1 vers GEODP 2</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>9623.1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PDMDEP-34216</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CHATEAUGIRON</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Migration GEODP Placier 2</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>875</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PDMDEP-34201</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Commune de Macon </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>GEODP Placier</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>554</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PDMDEP-34070</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>VILLE DE VANNES</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PDMDEP-33991</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>COMMUNE DE QUIMPERLE</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PDMDEP-33914</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Commune d'Arras</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Migration GEODP ODP (Terrasse)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>700</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PDMDEP-33850</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Commune de Nans les Pins</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>136</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PDMDEP-33605</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Commune de Trets</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PDMDEP-33401</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>COMMUNE DE MONTBELIARD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>1032</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PDMDEP-33245</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>MAIRIE DE LODEVE</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Migracier activité Placier vers Geodp V2</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>149</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PDMDEP-33177</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Commune de Bonneville</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PDMDEP-32974</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>COMMUNE DU PONTET</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Migration GeODP Placier 2/2</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PDMDEP-32741</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MAIRIE DE LA SENTINELLE</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Acquisition Geodp Caisse</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>305.6</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PDMDEP-32340</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Migration GEODP Placier </t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>BISCHWILLER</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PDMDEP-35636</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Estelle LEDUC</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>COMMUNE D'ANNEMASSE</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier) + Acquisition modules Voirie et Terrasses</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>1852.8</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PDMDEP-35478</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Estelle LEDUC</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>COMMUNE DE VENCE</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Migration GeODP Placier Terrasse</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>4399.5</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PDMDEP-35212</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Estelle LEDUC</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>VILLE DE BOULOGNE-BILLANCOURT</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Hébergement - Formation ODP - Accompagnement à distance</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>250.5</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PDMDEP-35139</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Estelle LEDUC</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>COMMUNE DE HARNES</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Migration de GEODP-Placier + remise en service CB (jamais installé ils payent deja un abo)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>1465.2</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PDMDEP-35114</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Estelle LEDUC</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>MAIRIE DE CARNAC</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Migration de GEODP-Placier simple</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>394</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PDMDEP-34791</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Estelle LEDUC</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MAIRIE DE SAINT-ISMIER</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>GEODP PLACIER</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>1073.25</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PDMDEP-34701</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Estelle LEDUC</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Commune du Tampon</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Migration GEODP Placier</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>2763.25</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PDMDEP-34683</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Estelle LEDUC</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Commune des Ponts de Ce</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Migration GEODP Placier</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>516</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PDMDEP-34666</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Estelle LEDUC</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Commune des Ponts de Ce</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Migration GEODP TLPE</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PDMDEP-34640</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Estelle LEDUC</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>acquisition geodp caisse</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>1620</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PDMDEP-34589</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Estelle LEDUC</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>COMMUNE DE RIEZ</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>MIGRATION GEODP PLACIER simple</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>936</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PDMDEP-34090</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Estelle LEDUC</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>COMMUNE DE ERQUY</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Migration GEODP 2 + Pax</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>177.5</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PDMDEP-34021</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Estelle LEDUC</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Migration module Placier</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>2696</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PDMDEP-33158</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Estelle LEDUC</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Migration GeODP</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>1047</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PDMDEP-32202</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Estelle LEDUC</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>COMMUNE DE MONTAUBAN</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Migration GEODP2</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>3240</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PDMDEP-32629</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>COMMUNE D'ANTIBES</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Modélisation LiEx</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>403.07</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>201.54</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PDMDEP-32556</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>VILLE DE CHALON SUR SAONE</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>142.1</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>120.78</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PDMDEP-29949</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>MAIRE DE PONTARLIER</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Mise en service Littéralis Expert + Options</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>204.14</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Basse</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v>30.62</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PDMDEP-35439</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Modélisation suite audit sur site</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>1470.38</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>PDMDEP-34722</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>VILLE DE VILLEURBANNE</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Crédits d'heure (14h)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>243.6</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>PDMDEP-34499</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CLICHY</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>344</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PDMDEP-34235</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>DIJON METROPOLE</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>GRC + Connecteur</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>2649.6</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PDMDEP-33944</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Commune de Thionville</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AME Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>1980</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PDMDEP-33817</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Modélisation Seyne S/ Mer</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>186.24</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>PDMDEP-33808</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Purge arrêtés temporaires</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>1890</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PDMDEP-33475</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>COMMUNE D AUCH</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>FDS Facture LiS</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>171.4</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PDMDEP-32406</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SAINT PIERRE (LA REUNION)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AME</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>LE PERREUX SUR MARNE</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>557.14</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>PDMDEP-27992</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Tarifs de redevance 1j</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>3016.08</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PDMDEP-31197</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>COMMUNE D HENDAYE</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Migration 1 activité GEODP2</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>PDMDEP-34054</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>COMMUNE DE NEUILLY SUR MARNE</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Migration GEODP PLACIER</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>2125</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>PDMDEP-28055</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>3919.06</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I70" s="3" t="n">
+        <v>1959.53</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PDMDEP-28204</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Pastell + Reprise</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>1790</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>1521.5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PDMDEP-31546</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>COMMUNE DE MONTELIMAR</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Modélisation LiEx</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>1088.5</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I72" s="3" t="n">
+        <v>544.25</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>PDMDEP-28206</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>CP + Directeur de projet</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>275</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v>233.75</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>PDMDEP-28175</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>401.54</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v>200.77</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>PDMDEP-30197</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>CD56</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Pastell</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v>195.5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>PDMDEP-31951</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>SSO/LDAP</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>PDMDEP-35652</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>VILLE DE GEX</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Migration Li STD vers LiEx</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>PDMDEP-35567</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>API Publication</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>895</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>PDMDEP-34979</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>VILLE DE SURESNES</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Migration LiEx vers new serveur + MV Test et Prod</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>PDMDEP-34929</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>AME multi-communes acheter par la CC</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>960</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>PDMDEP-33232</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>21 crédits d'heure</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>280</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>PDMDEP-33231</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>21 crédits d'heure</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>680</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>PDMDEP-32990</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>COMMUNE DE MONTELIMAR</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Interface Civil net finance</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>PDMDEP-32268</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>CA DU NIORTAIS</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Modélisation</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>910</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Valentin CAUJOLLE</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Migration Littéralis essentiel vers standard</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Autre</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL GÉNÉRAL</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="n">
+        <v>110752.15</v>
+      </c>
+      <c r="G87" s="6" t="n"/>
+      <c r="H87" s="6" t="n"/>
+      <c r="I87" s="7" t="n">
+        <v>15909.5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>Sous-totaux par CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Prévision brute (€)</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Prévision pondérée (€)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n">
+        <v>52784.3</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>10734.26</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>16049.1</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>4757.3</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="n">
+        <v>14487.75</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>352.94</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="n">
+        <v>2255</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>(non assigné)</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="n">
+        <v>895</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Estelle LEDUC</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="n">
+        <v>23831</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Valentin CAUJOLLE</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>Sous-totaux par solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Prévision brute (€)</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Prévision pondérée (€)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Autre</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="n">
+        <v>78870.3</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>10799.26</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="n">
+        <v>31431.85</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>5110.24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>